--- a/data/trans_camb/IP16B98-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16B98-Edad-trans_camb.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-38,75; 24,16</t>
+          <t>-38,84; 24,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-56,71; 6,41</t>
+          <t>-57,74; 0,77</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,49; 33,35</t>
+          <t>-39,61; 32,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-57,19; 6,85</t>
+          <t>-60,04; 0,68</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,47</t>
+          <t>0,0; 54,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,08</t>
+          <t>0,0; 43,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,81</t>
+          <t>0,0; 36,73</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 217,19</t>
+          <t>0,0; 120,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,44</t>
+          <t>0,0; 77,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,64</t>
+          <t>0,0; 58,05</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,52</t>
+          <t>0,0; 79,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,12</t>
+          <t>0,0; 46,45</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 344,58</t>
+          <t>0,0; 396,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 85,61</t>
+          <t>0,0; 86,77</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 19,86</t>
+          <t>-3,8; 19,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 16,6</t>
+          <t>-10,27; 16,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 12,75</t>
+          <t>-4,84; 12,24</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 25,59</t>
+          <t>-4,0; 25,06</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 19,74</t>
+          <t>-10,9; 19,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 15,21</t>
+          <t>-4,87; 14,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B98-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16B98-Edad-trans_camb.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-38,84; 24,03</t>
+          <t>-41,28; 23,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-57,74; 0,77</t>
+          <t>-57,11; 4,52</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,61; 32,44</t>
+          <t>-41,69; 32,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-60,04; 0,68</t>
+          <t>-57,81; 4,81</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,65</t>
+          <t>0,0; 69,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,59</t>
+          <t>0,0; 43,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,73</t>
+          <t>0,0; 31,0</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 120,51</t>
+          <t>0,0; 223,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,28</t>
+          <t>0,0; 77,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,05</t>
+          <t>0,0; 44,92</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,88</t>
+          <t>0,0; 78,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,45</t>
+          <t>0,0; 46,34</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 396,94</t>
+          <t>0,0; 363,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 86,77</t>
+          <t>0,0; 86,37</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 19,37</t>
+          <t>-2,67; 19,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 16,64</t>
+          <t>-10,52; 15,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 12,24</t>
+          <t>-5,36; 12,75</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 25,06</t>
+          <t>-2,67; 24,38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 19,98</t>
+          <t>-11,2; 18,96</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 14,21</t>
+          <t>-5,57; 15,08</t>
         </is>
       </c>
     </row>
